--- a/基本設計/18_業務ルールと状態遷移_基本設計書.xlsx
+++ b/基本設計/18_業務ルールと状態遷移_基本設計書.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R90f1ad1833d44340"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rf2bdea2102e24eec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_ステータス定義" sheetId="27" r:id="R6a4e450f07f64556"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_タスク状態遷移" sheetId="28" r:id="Rf534d57e0f7e47c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28_業務ルール" sheetId="29" r:id="R1ed23fe9b53640c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rdc09cc60a96a405e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R980c49ac104943d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_ステータス定義" sheetId="27" r:id="Rf16e4c6aca11437f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_タスク状態遷移" sheetId="28" r:id="Rae94418b06234121"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28_業務ルール" sheetId="29" r:id="Rca219279557147f2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1101,10 +1101,7 @@
       <x:c r="F16" s="140"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1119,25 +1116,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="182" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="182"/>
-      <x:c r="D19" s="182"/>
-      <x:c r="E19" s="182"/>
-      <x:c r="F19" s="182"/>
-      <x:c r="G19" s="182"/>
-      <x:c r="H19" s="182"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="182"/>
-      <x:c r="C20" s="182"/>
-      <x:c r="D20" s="182"/>
-      <x:c r="E20" s="182"/>
-      <x:c r="F20" s="182"/>
-      <x:c r="G20" s="182"/>
-      <x:c r="H20" s="182"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="182"/>
